--- a/artfynd/A 40302-2022 artfynd.xlsx
+++ b/artfynd/A 40302-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40302-2022 artfynd.xlsx
+++ b/artfynd/A 40302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82453647</v>
+        <v>82451292</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100087</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540748.7496952132</v>
+        <v>540766</v>
       </c>
       <c r="R2" t="n">
-        <v>6357333.134600981</v>
+        <v>6357333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
+          <t>2019-06-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -811,15 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82449655</v>
+        <v>82455832</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,26 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -870,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540748.7496952132</v>
+        <v>540766</v>
       </c>
       <c r="R3" t="n">
-        <v>6357333.134600981</v>
+        <v>6357333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +890,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
+          <t>2019-06-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -910,7 +900,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -947,42 +937,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82447921</v>
+        <v>82449654</v>
       </c>
       <c r="B4" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1006,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540748.7496952132</v>
+        <v>540766</v>
       </c>
       <c r="R4" t="n">
-        <v>6357333.134600981</v>
+        <v>6357333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +1021,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
+          <t>2019-06-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1046,7 +1031,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1080,6 +1065,530 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>82449655</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Målilla, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>540749</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6357333</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gårdveda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-08-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-08-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal lada mitt i skogen</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>82453646</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Målilla, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>540766</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6357333</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gårdveda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-06-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal lada mitt i skogen</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>82453647</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Målilla, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>540749</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6357333</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gårdveda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-08-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-08-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal lada mitt i skogen</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>82447921</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Målilla, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>540749</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6357333</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gårdveda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-08-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-08-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal lada mitt i skogen</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40302-2022 artfynd.xlsx
+++ b/artfynd/A 40302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82451292</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82455832</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,6 +1080,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82449654</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1196,6 +1216,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82449655</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1327,6 +1352,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82453646</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1458,6 +1488,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82453647</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1589,8 +1624,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82447921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>